--- a/_stats_outputs/spline_coefs.xlsx
+++ b/_stats_outputs/spline_coefs.xlsx
@@ -403,13 +403,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.2110101010100996</v>
+        <v>-6.423147474747493</v>
       </c>
       <c r="E2">
-        <v>0.04450954772451955</v>
+        <v>1.354914252058493</v>
       </c>
       <c r="F2">
-        <v>1.580848788651574E-05</v>
+        <v>1.583446996533682E-05</v>
       </c>
     </row>
     <row r="3">
@@ -429,13 +429,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08973856209150334</v>
+        <v>-2.731641830065347</v>
       </c>
       <c r="E3">
-        <v>0.04166084084237619</v>
+        <v>1.268204305637989</v>
       </c>
       <c r="F3">
-        <v>0.03675158210273577</v>
+        <v>0.03676246612519982</v>
       </c>
     </row>
     <row r="4">
@@ -455,13 +455,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0649131944444435</v>
+        <v>-1.975957638888928</v>
       </c>
       <c r="E4">
-        <v>0.04357240238435052</v>
+        <v>1.326389035358704</v>
       </c>
       <c r="F4">
-        <v>0.1424642154395795</v>
+        <v>0.1424818461087866</v>
       </c>
     </row>
     <row r="5">
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.07379629629629628</v>
+        <v>-2.246359259259249</v>
       </c>
       <c r="E5">
-        <v>0.04577274053779708</v>
+        <v>1.39336391509817</v>
       </c>
       <c r="F5">
-        <v>0.1122475609828154</v>
+        <v>0.1122616856800545</v>
       </c>
     </row>
     <row r="6">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.1388095238095226</v>
+        <v>-4.225361904761913</v>
       </c>
       <c r="E6">
-        <v>0.04832543806782964</v>
+        <v>1.471064384295108</v>
       </c>
       <c r="F6">
-        <v>0.005411073553073942</v>
+        <v>0.005413122268435194</v>
       </c>
     </row>
     <row r="7">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.04171717171717153</v>
+        <v>-1.269870707070732</v>
       </c>
       <c r="E7">
-        <v>0.04450954772451957</v>
+        <v>1.354914252058493</v>
       </c>
       <c r="F7">
-        <v>0.3527763124143238</v>
+        <v>0.3527945595415014</v>
       </c>
     </row>
     <row r="8">
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.02447712418300582</v>
+        <v>-0.7450836601306867</v>
       </c>
       <c r="E8">
-        <v>0.04166084084237622</v>
+        <v>1.268204305637988</v>
       </c>
       <c r="F8">
-        <v>0.5598470440139343</v>
+        <v>0.5598641011590373</v>
       </c>
     </row>
     <row r="9">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.1003645833333334</v>
+        <v>-3.055097916666678</v>
       </c>
       <c r="E9">
-        <v>0.04357240238435051</v>
+        <v>1.326389035358704</v>
       </c>
       <c r="F9">
-        <v>0.02538354633540935</v>
+        <v>0.02539127726320382</v>
       </c>
     </row>
     <row r="10">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.06696296296296286</v>
+        <v>-2.038352592592594</v>
       </c>
       <c r="E10">
-        <v>0.04577274053779708</v>
+        <v>1.39336391509817</v>
       </c>
       <c r="F10">
-        <v>0.1487889533888876</v>
+        <v>0.1488044793878647</v>
       </c>
     </row>
     <row r="11">
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.1720634920634913</v>
+        <v>-5.237612698412692</v>
       </c>
       <c r="E11">
-        <v>0.04832543806782963</v>
+        <v>1.471064384295108</v>
       </c>
       <c r="F11">
-        <v>0.0006763539190523852</v>
+        <v>0.0006767880293531032</v>
       </c>
     </row>
     <row r="12">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.03154761904761876</v>
+        <v>0.9603095238094982</v>
       </c>
       <c r="E12">
-        <v>0.04463064807407042</v>
+        <v>1.358575983643928</v>
       </c>
       <c r="F12">
-        <v>0.4822995689550592</v>
+        <v>0.4823056198352992</v>
       </c>
     </row>
     <row r="13">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.003406432748538793</v>
+        <v>0.1036918128655163</v>
       </c>
       <c r="E13">
-        <v>0.04611349259134993</v>
+        <v>1.403714383341988</v>
       </c>
       <c r="F13">
-        <v>0.9413300853787913</v>
+        <v>0.9413309006692685</v>
       </c>
     </row>
     <row r="14">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.1426909722222235</v>
+        <v>-4.34351319444447</v>
       </c>
       <c r="E14">
-        <v>0.0531445736535525</v>
+        <v>1.617743403229631</v>
       </c>
       <c r="F14">
-        <v>0.008543478815839977</v>
+        <v>0.008544345759430824</v>
       </c>
     </row>
     <row r="15">
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.4488095238095233</v>
+        <v>-13.66176190476191</v>
       </c>
       <c r="E15">
-        <v>0.05965619215900139</v>
+        <v>1.815959776183248</v>
       </c>
       <c r="F15">
-        <v>1.112876826520029E-11</v>
+        <v>1.113432072774402E-11</v>
       </c>
     </row>
     <row r="16">
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.008333333333333401</v>
+        <v>0.253666666666678</v>
       </c>
       <c r="E16">
-        <v>0.05965619215900142</v>
+        <v>1.81595977618325</v>
       </c>
       <c r="F16">
-        <v>0.8891414350193021</v>
+        <v>0.8891429660690766</v>
       </c>
     </row>
     <row r="17">
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.01369047619047656</v>
+        <v>0.4167380952380832</v>
       </c>
       <c r="E17">
-        <v>0.04463064807407041</v>
+        <v>1.358575983643928</v>
       </c>
       <c r="F17">
-        <v>0.760060255368285</v>
+        <v>0.7600634886814621</v>
       </c>
     </row>
     <row r="18">
@@ -819,13 +819,13 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.03385964912280707</v>
+        <v>1.030687719298265</v>
       </c>
       <c r="E18">
-        <v>0.04611349259134994</v>
+        <v>1.403714383341989</v>
       </c>
       <c r="F18">
-        <v>0.4653087153728432</v>
+        <v>0.4653148823652857</v>
       </c>
     </row>
     <row r="19">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.1635069444444441</v>
+        <v>-4.977151388888924</v>
       </c>
       <c r="E19">
-        <v>0.0531445736535525</v>
+        <v>1.617743403229631</v>
       </c>
       <c r="F19">
-        <v>0.002726409438047479</v>
+        <v>0.002726754893905292</v>
       </c>
     </row>
     <row r="20">
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.3503571428571429</v>
+        <v>-10.6648714285714</v>
       </c>
       <c r="E20">
-        <v>0.05965619215900141</v>
+        <v>1.815959776183248</v>
       </c>
       <c r="F20">
-        <v>3.965219826111451E-08</v>
+        <v>3.966656527763416E-08</v>
       </c>
     </row>
     <row r="21">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.03174603174603151</v>
+        <v>-0.9663492063492147</v>
       </c>
       <c r="E21">
-        <v>0.05965619215900142</v>
+        <v>1.81595977618325</v>
       </c>
       <c r="F21">
-        <v>0.5956136611006256</v>
+        <v>0.5956187662874811</v>
       </c>
     </row>
     <row r="22">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.1176851851851839</v>
+        <v>3.582337037036986</v>
       </c>
       <c r="E22">
-        <v>0.1117526506598604</v>
+        <v>3.402732579890376</v>
       </c>
       <c r="F22">
-        <v>0.2937591064226305</v>
+        <v>0.2938978084990642</v>
       </c>
     </row>
     <row r="23">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.06491228070175481</v>
+        <v>1.975929824561435</v>
       </c>
       <c r="E23">
-        <v>0.05325448209803618</v>
+        <v>1.619746536508845</v>
       </c>
       <c r="F23">
-        <v>0.2260509887262928</v>
+        <v>0.2256133061324169</v>
       </c>
     </row>
     <row r="24">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.324201388888889</v>
+        <v>-9.868690277777795</v>
       </c>
       <c r="E24">
-        <v>0.06182544098537009</v>
+        <v>1.881127293536659</v>
       </c>
       <c r="F24">
-        <v>6.842078419897531E-07</v>
+        <v>6.651944596423631E-07</v>
       </c>
     </row>
     <row r="25">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.2165674603174607</v>
+        <v>-6.59231349206349</v>
       </c>
       <c r="E25">
-        <v>0.06971722888155484</v>
+        <v>2.121726099912245</v>
       </c>
       <c r="F25">
-        <v>0.002292314579787002</v>
+        <v>0.002283487725152483</v>
       </c>
     </row>
     <row r="26">
@@ -1027,13 +1027,13 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.002837301587301787</v>
+        <v>-0.08636746031747317</v>
       </c>
       <c r="E26">
-        <v>0.06971722888155486</v>
+        <v>2.121726099912246</v>
       </c>
       <c r="F26">
-        <v>0.9675950475200679</v>
+        <v>0.9675873929345102</v>
       </c>
     </row>
     <row r="27">
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.2852314814814819</v>
+        <v>8.682446296296266</v>
       </c>
       <c r="E27">
-        <v>0.1117526506598604</v>
+        <v>3.402732579890376</v>
       </c>
       <c r="F27">
-        <v>0.01155812487558691</v>
+        <v>0.01158157140388199</v>
       </c>
     </row>
     <row r="28">
@@ -1079,13 +1079,13 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.03080409356725098</v>
+        <v>0.9376766081871577</v>
       </c>
       <c r="E28">
-        <v>0.05325448209803617</v>
+        <v>1.619746536508845</v>
       </c>
       <c r="F28">
-        <v>0.5644110402649873</v>
+        <v>0.5640658167087238</v>
       </c>
     </row>
     <row r="29">
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.2828472222222219</v>
+        <v>-8.609869444444458</v>
       </c>
       <c r="E29">
-        <v>0.06182544098537007</v>
+        <v>1.88112729353666</v>
       </c>
       <c r="F29">
-        <v>1.168169195295081E-05</v>
+        <v>1.145578380860758E-05</v>
       </c>
     </row>
     <row r="30">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.2019047619047621</v>
+        <v>-6.145980952380953</v>
       </c>
       <c r="E30">
-        <v>0.06971722888155485</v>
+        <v>2.121726099912246</v>
       </c>
       <c r="F30">
-        <v>0.004384402273547854</v>
+        <v>0.004370207762788571</v>
       </c>
     </row>
     <row r="31">
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.01662698412698442</v>
+        <v>-0.5061253968253976</v>
       </c>
       <c r="E31">
-        <v>0.06971722888155486</v>
+        <v>2.121726099912246</v>
       </c>
       <c r="F31">
-        <v>0.8118474603482295</v>
+        <v>0.8118036647322855</v>
       </c>
     </row>
     <row r="32">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.2039087301587311</v>
+        <v>-6.206981746031684</v>
       </c>
       <c r="E32">
-        <v>0.04254364044319818</v>
+        <v>1.29502832210912</v>
       </c>
       <c r="F32">
-        <v>3.157715116614428E-06</v>
+        <v>3.157708996538866E-06</v>
       </c>
     </row>
     <row r="33">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="D33">
-        <v>-0.04663742690058437</v>
+        <v>-1.419643274853835</v>
       </c>
       <c r="E33">
-        <v>0.0440066552541822</v>
+        <v>1.339562528467895</v>
       </c>
       <c r="F33">
-        <v>0.2904884401819666</v>
+        <v>0.2904884190811925</v>
       </c>
     </row>
     <row r="34">
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.1857118055555554</v>
+        <v>5.65306736111113</v>
       </c>
       <c r="E34">
-        <v>0.05092466938505459</v>
+        <v>1.55014703172793</v>
       </c>
       <c r="F34">
-        <v>0.0003367519758260206</v>
+        <v>0.0003367522854410832</v>
       </c>
     </row>
     <row r="35">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="D35">
-        <v>-0.3387301587301593</v>
+        <v>-10.310946031746</v>
       </c>
       <c r="E35">
-        <v>0.05731075370339267</v>
+        <v>1.744539563613628</v>
       </c>
       <c r="F35">
-        <v>1.43885439632609E-08</v>
+        <v>1.438861321125171E-08</v>
       </c>
     </row>
     <row r="36">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="D36">
-        <v>-0.05353174603174547</v>
+        <v>-1.629506349206341</v>
       </c>
       <c r="E36">
-        <v>0.05731075370339263</v>
+        <v>1.744539563613629</v>
       </c>
       <c r="F36">
-        <v>0.3513912027358138</v>
+        <v>0.3513912644002349</v>
       </c>
     </row>
     <row r="37">
@@ -1313,13 +1313,13 @@
         </is>
       </c>
       <c r="D37">
-        <v>-0.2188293650793645</v>
+        <v>-6.661165873015835</v>
       </c>
       <c r="E37">
-        <v>0.04254364044319818</v>
+        <v>1.29502832210912</v>
       </c>
       <c r="F37">
-        <v>6.294180243981545E-07</v>
+        <v>6.294166080466655E-07</v>
       </c>
     </row>
     <row r="38">
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="D38">
-        <v>-0.124195906432749</v>
+        <v>-3.780523391812936</v>
       </c>
       <c r="E38">
-        <v>0.04400665525418219</v>
+        <v>1.339562528467895</v>
       </c>
       <c r="F38">
-        <v>0.005237908390925802</v>
+        <v>0.005237906310456354</v>
       </c>
     </row>
     <row r="39">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.1117708333333334</v>
+        <v>3.402304166666673</v>
       </c>
       <c r="E39">
-        <v>0.05092466938505456</v>
+        <v>1.550147031727929</v>
       </c>
       <c r="F39">
-        <v>0.02929967444597402</v>
+        <v>0.02929968479562937</v>
       </c>
     </row>
     <row r="40">
@@ -1391,13 +1391,13 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.217777777777778</v>
+        <v>-6.629155555555537</v>
       </c>
       <c r="E40">
-        <v>0.05731075370339266</v>
+        <v>1.744539563613628</v>
       </c>
       <c r="F40">
-        <v>0.000191681342519255</v>
+        <v>0.0001916817270550657</v>
       </c>
     </row>
     <row r="41">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="D41">
-        <v>-0.1114880952380947</v>
+        <v>-3.393697619047634</v>
       </c>
       <c r="E41">
-        <v>0.05731075370339263</v>
+        <v>1.744539563613629</v>
       </c>
       <c r="F41">
-        <v>0.05312810981925954</v>
+        <v>0.05312814066743252</v>
       </c>
     </row>
     <row r="42">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="D42">
-        <v>-0.0667708333333359</v>
+        <v>-2.032504166666675</v>
       </c>
       <c r="E42">
-        <v>0.1510787129238844</v>
+        <v>4.598046080824992</v>
       </c>
       <c r="F42">
-        <v>0.6633000990428082</v>
+        <v>0.6632360165721798</v>
       </c>
     </row>
     <row r="43">
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.07437908496731889</v>
+        <v>2.264099346405465</v>
       </c>
       <c r="E43">
-        <v>0.1251757535869159</v>
+        <v>3.809343135714936</v>
       </c>
       <c r="F43">
-        <v>0.5660834757143449</v>
+        <v>0.5659577342644913</v>
       </c>
     </row>
     <row r="44">
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="D44">
-        <v>-0.429409722222225</v>
+        <v>-13.07123194444445</v>
       </c>
       <c r="E44">
-        <v>0.1280715757411388</v>
+        <v>3.897520077689471</v>
       </c>
       <c r="F44">
-        <v>0.006836281073534234</v>
+        <v>0.006808827826425278</v>
       </c>
     </row>
     <row r="45">
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.06796296296296143</v>
+        <v>2.068792592592777</v>
       </c>
       <c r="E45">
-        <v>0.1314807942704531</v>
+        <v>4.001328354581855</v>
       </c>
       <c r="F45">
-        <v>0.6148861183567154</v>
+        <v>0.614784803339642</v>
       </c>
     </row>
     <row r="46">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D46">
-        <v>-0.2185714285714309</v>
+        <v>-6.653314285714222</v>
       </c>
       <c r="E46">
-        <v>0.1355300126349668</v>
+        <v>4.124622308310929</v>
       </c>
       <c r="F46">
-        <v>0.1305997022802535</v>
+        <v>0.130475011948487</v>
       </c>
     </row>
     <row r="47">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="D47">
-        <v>-0.1515277777777745</v>
+        <v>-4.612505555555496</v>
       </c>
       <c r="E47">
-        <v>0.1510787129238845</v>
+        <v>4.598046080824997</v>
       </c>
       <c r="F47">
-        <v>0.3279570445978285</v>
+        <v>0.3278506577736185</v>
       </c>
     </row>
     <row r="48">
@@ -1599,13 +1599,13 @@
         </is>
       </c>
       <c r="D48">
-        <v>0.02089869281045837</v>
+        <v>0.6361562091505459</v>
       </c>
       <c r="E48">
-        <v>0.1251757535869161</v>
+        <v>3.809343135714943</v>
       </c>
       <c r="F48">
-        <v>0.8708608539939052</v>
+        <v>0.8708207645947371</v>
       </c>
     </row>
     <row r="49">
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="D49">
-        <v>-0.3478645833333313</v>
+        <v>-10.58899791666659</v>
       </c>
       <c r="E49">
-        <v>0.1280715757411388</v>
+        <v>3.897520077689479</v>
       </c>
       <c r="F49">
-        <v>0.02079878020225711</v>
+        <v>0.02074151595958575</v>
       </c>
     </row>
     <row r="50">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="D50">
-        <v>0.09777777777777955</v>
+        <v>2.976355555555768</v>
       </c>
       <c r="E50">
-        <v>0.1314807942704533</v>
+        <v>4.001328354581861</v>
       </c>
       <c r="F50">
-        <v>0.4717981590417663</v>
+        <v>0.471667503646514</v>
       </c>
     </row>
     <row r="51">
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="D51">
-        <v>0.1135515873015892</v>
+        <v>3.456510317460414</v>
       </c>
       <c r="E51">
-        <v>0.1355300126349669</v>
+        <v>4.124622308310936</v>
       </c>
       <c r="F51">
-        <v>0.4171323288768002</v>
+        <v>0.4170025926556159</v>
       </c>
     </row>
     <row r="52">
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="D52">
-        <v>-0.2634595959595948</v>
+        <v>-8.019710101010029</v>
       </c>
       <c r="E52">
-        <v>0.07076059282784201</v>
+        <v>2.153951507108144</v>
       </c>
       <c r="F52">
-        <v>0.0002538197519029318</v>
+        <v>0.0002538180037610024</v>
       </c>
     </row>
     <row r="53">
@@ -1729,13 +1729,13 @@
         </is>
       </c>
       <c r="D53">
-        <v>-0.02888888888888938</v>
+        <v>-0.8793777777778189</v>
       </c>
       <c r="E53">
-        <v>0.06574989085737991</v>
+        <v>2.001419572024964</v>
       </c>
       <c r="F53">
-        <v>0.6608531525427964</v>
+        <v>0.6608520094689647</v>
       </c>
     </row>
     <row r="54">
@@ -1755,13 +1755,13 @@
         </is>
       </c>
       <c r="D54">
-        <v>-0.09249999999999874</v>
+        <v>-2.815700000000034</v>
       </c>
       <c r="E54">
-        <v>0.07297153363237513</v>
+        <v>2.221255125289048</v>
       </c>
       <c r="F54">
-        <v>0.2063659314878084</v>
+        <v>0.2063662737295266</v>
       </c>
     </row>
     <row r="55">
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.09001736111111137</v>
+        <v>2.740128472222248</v>
       </c>
       <c r="E55">
-        <v>0.06911619466278951</v>
+        <v>2.103894054710557</v>
       </c>
       <c r="F55">
-        <v>0.1942332681517829</v>
+        <v>0.1942326367005708</v>
       </c>
     </row>
     <row r="56">
@@ -1807,13 +1807,13 @@
         </is>
       </c>
       <c r="D56">
-        <v>0.006845238095238481</v>
+        <v>0.2083690476190498</v>
       </c>
       <c r="E56">
-        <v>0.0774220462816398</v>
+        <v>2.356733701423989</v>
       </c>
       <c r="F56">
-        <v>0.9296334215271262</v>
+        <v>0.9296336201619528</v>
       </c>
     </row>
     <row r="57">
@@ -1833,13 +1833,13 @@
         </is>
       </c>
       <c r="D57">
-        <v>-0.1872727272727272</v>
+        <v>-5.700581818181795</v>
       </c>
       <c r="E57">
-        <v>0.07076059282784201</v>
+        <v>2.153951507108143</v>
       </c>
       <c r="F57">
-        <v>0.008759525948556697</v>
+        <v>0.008759494820790671</v>
       </c>
     </row>
     <row r="58">
@@ -1859,13 +1859,13 @@
         </is>
       </c>
       <c r="D58">
-        <v>0.003153594771242509</v>
+        <v>0.09599542483659614</v>
       </c>
       <c r="E58">
-        <v>0.06574989085737989</v>
+        <v>2.001419572024964</v>
       </c>
       <c r="F58">
-        <v>0.9617921146403856</v>
+        <v>0.961791977599322</v>
       </c>
     </row>
     <row r="59">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="D59">
-        <v>-0.04657407407407368</v>
+        <v>-1.417714814814846</v>
       </c>
       <c r="E59">
-        <v>0.07297153363237513</v>
+        <v>2.221255125289048</v>
       </c>
       <c r="F59">
-        <v>0.5240201093817065</v>
+        <v>0.5240204198230849</v>
       </c>
     </row>
     <row r="60">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="D60">
-        <v>-0.003541666666666925</v>
+        <v>-0.1078083333333336</v>
       </c>
       <c r="E60">
-        <v>0.06911619466278951</v>
+        <v>2.103894054710558</v>
       </c>
       <c r="F60">
-        <v>0.9591822198390091</v>
+        <v>0.9591821628372402</v>
       </c>
     </row>
     <row r="61">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="D61">
-        <v>-0.09275793650793591</v>
+        <v>-2.823551587301576</v>
       </c>
       <c r="E61">
-        <v>0.0774220462816398</v>
+        <v>2.356733701423989</v>
       </c>
       <c r="F61">
-        <v>0.2322675770598399</v>
+        <v>0.2322689101984859</v>
       </c>
     </row>
   </sheetData>
